--- a/TLC_COL/TLC_COL/TLC COL DiagramaGantt.xlsx
+++ b/TLC_COL/TLC_COL/TLC COL DiagramaGantt.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\laura\OneDrive\Escritorio\BOOTCAMP JULIO\TLC_COL\TLC_COL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88E69957-02B2-40C9-A637-25EFC12A2C34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2E08138-7805-433E-98CC-6B42365D2FB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
   <si>
     <t>Assignees</t>
   </si>
@@ -104,6 +104,15 @@
   <si>
     <t>TLC COL</t>
   </si>
+  <si>
+    <t>SPRINT 1</t>
+  </si>
+  <si>
+    <t>SPRINT 2</t>
+  </si>
+  <si>
+    <t>SPRINT 3</t>
+  </si>
 </sst>
 </file>
 
@@ -112,7 +121,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd\.mm\.yyyy"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -179,8 +188,15 @@
       <name val="Verdana"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -201,12 +217,54 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.39997558519241921"/>
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor rgb="FFF3F3F3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor rgb="FFF3F3F3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor rgb="FFF3F3F3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor rgb="FFF3F3F3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="16">
+  <borders count="34">
     <border>
       <left/>
       <right/>
@@ -323,51 +381,6 @@
       <left style="medium">
         <color indexed="64"/>
       </left>
-      <right style="thin">
-        <color rgb="FF999999"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF999999"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF999999"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF999999"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF999999"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF999999"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF999999"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
       <right style="medium">
         <color indexed="64"/>
       </right>
@@ -376,21 +389,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF999999"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF999999"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -437,55 +435,411 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF999999"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF999999"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF999999"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF999999"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF999999"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF999999"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF999999"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF999999"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF999999"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF999999"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF999999"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF999999"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF999999"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF999999"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF999999"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF999999"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF999999"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF999999"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF999999"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF999999"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF999999"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF999999"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -840,7 +1194,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:AE1001"/>
+  <dimension ref="A1:AE1002"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.453125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.26953125" customWidth="1"/>
@@ -850,457 +1204,489 @@
   <sheetData>
     <row r="1" spans="1:31" ht="91.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1"/>
-      <c r="B1" s="27" t="s">
+      <c r="B1" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="7"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-      <c r="O1" s="6"/>
-      <c r="P1" s="6"/>
-      <c r="Q1" s="6"/>
-      <c r="R1" s="6"/>
-      <c r="S1" s="6"/>
-      <c r="T1" s="6"/>
-      <c r="U1" s="6"/>
-      <c r="V1" s="6"/>
-      <c r="W1" s="6"/>
-      <c r="X1" s="6"/>
-      <c r="Y1" s="6"/>
-      <c r="Z1" s="6"/>
-      <c r="AA1" s="6"/>
-      <c r="AB1" s="6"/>
-      <c r="AC1" s="6"/>
-    </row>
-    <row r="2" spans="1:31" ht="65" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="4"/>
-      <c r="B2" s="30" t="s">
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
+      <c r="M1" s="15"/>
+      <c r="N1" s="15"/>
+      <c r="O1" s="15"/>
+      <c r="P1" s="15"/>
+      <c r="Q1" s="15"/>
+      <c r="R1" s="15"/>
+      <c r="S1" s="15"/>
+      <c r="T1" s="15"/>
+      <c r="U1" s="15"/>
+      <c r="V1" s="15"/>
+      <c r="W1" s="15"/>
+      <c r="X1" s="15"/>
+      <c r="Y1" s="15"/>
+      <c r="Z1" s="15"/>
+      <c r="AA1" s="15"/>
+      <c r="AB1" s="15"/>
+      <c r="AC1" s="15"/>
+    </row>
+    <row r="2" spans="1:31" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="1"/>
+      <c r="B2" s="9"/>
+      <c r="C2" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="21"/>
+      <c r="G2" s="21"/>
+      <c r="H2" s="22"/>
+      <c r="I2" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="J2" s="24"/>
+      <c r="K2" s="24"/>
+      <c r="L2" s="24"/>
+      <c r="M2" s="24"/>
+      <c r="N2" s="24"/>
+      <c r="O2" s="24"/>
+      <c r="P2" s="24"/>
+      <c r="Q2" s="24"/>
+      <c r="R2" s="24"/>
+      <c r="S2" s="24"/>
+      <c r="T2" s="24"/>
+      <c r="U2" s="24"/>
+      <c r="V2" s="24"/>
+      <c r="W2" s="25"/>
+      <c r="X2" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="Y2" s="27"/>
+      <c r="Z2" s="27"/>
+      <c r="AA2" s="28"/>
+    </row>
+    <row r="3" spans="1:31" ht="65" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="4"/>
+      <c r="B3" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="17">
+      <c r="C3" s="34">
         <v>45829</v>
       </c>
-      <c r="D2" s="17">
+      <c r="D3" s="6">
         <v>45834</v>
       </c>
-      <c r="E2" s="17">
+      <c r="E3" s="6">
         <v>45836</v>
       </c>
-      <c r="F2" s="17">
+      <c r="F3" s="6">
         <v>45841</v>
       </c>
-      <c r="G2" s="17">
+      <c r="G3" s="6">
         <v>45843</v>
       </c>
-      <c r="H2" s="17">
+      <c r="H3" s="7">
         <v>45848</v>
       </c>
-      <c r="I2" s="17">
+      <c r="I3" s="34">
         <v>45850</v>
       </c>
-      <c r="J2" s="17">
+      <c r="J3" s="6">
         <v>45855</v>
       </c>
-      <c r="K2" s="17">
+      <c r="K3" s="6">
         <v>45857</v>
       </c>
-      <c r="L2" s="17">
+      <c r="L3" s="6">
         <v>45862</v>
       </c>
-      <c r="M2" s="17">
+      <c r="M3" s="6">
         <v>45864</v>
       </c>
-      <c r="N2" s="17">
+      <c r="N3" s="6">
         <v>45869</v>
       </c>
-      <c r="O2" s="17">
+      <c r="O3" s="6">
         <v>45871</v>
       </c>
-      <c r="P2" s="17">
+      <c r="P3" s="6">
         <v>45876</v>
       </c>
-      <c r="Q2" s="17">
+      <c r="Q3" s="6">
         <v>45878</v>
       </c>
-      <c r="R2" s="17">
+      <c r="R3" s="6">
         <v>45883</v>
       </c>
-      <c r="S2" s="17">
+      <c r="S3" s="6">
         <v>45885</v>
       </c>
-      <c r="T2" s="17">
+      <c r="T3" s="6">
         <v>45890</v>
       </c>
-      <c r="U2" s="17">
+      <c r="U3" s="6">
         <v>45892</v>
       </c>
-      <c r="V2" s="17">
+      <c r="V3" s="6">
         <v>45897</v>
       </c>
-      <c r="W2" s="17">
+      <c r="W3" s="7">
         <v>45899</v>
       </c>
-      <c r="X2" s="17">
+      <c r="X3" s="34">
         <v>45904</v>
       </c>
-      <c r="Y2" s="17">
+      <c r="Y3" s="6">
         <v>45906</v>
       </c>
-      <c r="Z2" s="17">
+      <c r="Z3" s="6">
         <v>45911</v>
       </c>
-      <c r="AA2" s="17">
+      <c r="AA3" s="7">
         <v>45913</v>
       </c>
-      <c r="AB2" s="17">
+      <c r="AB3" s="33">
         <v>45918</v>
       </c>
-      <c r="AC2" s="18">
+      <c r="AC3" s="7">
         <v>45920</v>
       </c>
-    </row>
-    <row r="3" spans="1:31" ht="13.5" x14ac:dyDescent="0.3">
-      <c r="A3" s="1"/>
-      <c r="B3" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" s="19"/>
-      <c r="D3" s="20"/>
-      <c r="E3" s="21"/>
-      <c r="F3" s="20"/>
-      <c r="G3" s="20"/>
-      <c r="H3" s="20"/>
-      <c r="I3" s="20"/>
-      <c r="J3" s="20"/>
-      <c r="K3" s="20"/>
-      <c r="L3" s="20"/>
-      <c r="M3" s="20"/>
-      <c r="N3" s="20"/>
-      <c r="O3" s="20"/>
-      <c r="P3" s="20"/>
-      <c r="Q3" s="20"/>
-      <c r="R3" s="20"/>
-      <c r="S3" s="20"/>
-      <c r="T3" s="20"/>
-      <c r="U3" s="20"/>
-      <c r="V3" s="20"/>
-      <c r="W3" s="20"/>
-      <c r="X3" s="20"/>
-      <c r="Y3" s="20"/>
-      <c r="Z3" s="20"/>
-      <c r="AA3" s="20"/>
-      <c r="AB3" s="20"/>
-      <c r="AC3" s="22"/>
     </row>
     <row r="4" spans="1:31" ht="13.5" x14ac:dyDescent="0.3">
       <c r="A4" s="1"/>
-      <c r="B4" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="23"/>
-      <c r="D4" s="5"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="8"/>
-      <c r="G4" s="5"/>
-      <c r="H4" s="5"/>
-      <c r="I4" s="5"/>
-      <c r="J4" s="5"/>
-      <c r="K4" s="5"/>
-      <c r="L4" s="5"/>
-      <c r="M4" s="5"/>
-      <c r="N4" s="5"/>
-      <c r="O4" s="5"/>
-      <c r="P4" s="5"/>
-      <c r="Q4" s="5"/>
-      <c r="R4" s="5"/>
-      <c r="S4" s="8"/>
-      <c r="T4" s="8"/>
-      <c r="U4" s="5"/>
-      <c r="V4" s="5"/>
-      <c r="W4" s="5"/>
-      <c r="X4" s="5"/>
-      <c r="Y4" s="5"/>
-      <c r="Z4" s="5"/>
-      <c r="AA4" s="5"/>
-      <c r="AB4" s="5"/>
-      <c r="AC4" s="9"/>
+      <c r="B4" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="70"/>
+      <c r="D4" s="29"/>
+      <c r="E4" s="29"/>
+      <c r="F4" s="29"/>
+      <c r="G4" s="29"/>
+      <c r="H4" s="71"/>
+      <c r="I4" s="55"/>
+      <c r="J4" s="53"/>
+      <c r="K4" s="53"/>
+      <c r="L4" s="53"/>
+      <c r="M4" s="53"/>
+      <c r="N4" s="53"/>
+      <c r="O4" s="53"/>
+      <c r="P4" s="53"/>
+      <c r="Q4" s="53"/>
+      <c r="R4" s="53"/>
+      <c r="S4" s="53"/>
+      <c r="T4" s="53"/>
+      <c r="U4" s="53"/>
+      <c r="V4" s="53"/>
+      <c r="W4" s="54"/>
+      <c r="X4" s="55"/>
+      <c r="Y4" s="53"/>
+      <c r="Z4" s="53"/>
+      <c r="AA4" s="54"/>
+      <c r="AB4" s="56"/>
+      <c r="AC4" s="54"/>
     </row>
     <row r="5" spans="1:31" ht="13.5" x14ac:dyDescent="0.3">
       <c r="A5" s="1"/>
-      <c r="B5" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" s="23"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
-      <c r="I5" s="5"/>
-      <c r="J5" s="8"/>
-      <c r="K5" s="8"/>
-      <c r="L5" s="5"/>
-      <c r="M5" s="5"/>
-      <c r="N5" s="5"/>
-      <c r="O5" s="8"/>
-      <c r="P5" s="8"/>
-      <c r="Q5" s="5"/>
-      <c r="R5" s="5"/>
-      <c r="S5" s="8"/>
-      <c r="T5" s="8"/>
-      <c r="U5" s="5"/>
-      <c r="V5" s="5"/>
-      <c r="W5" s="5"/>
-      <c r="X5" s="5"/>
-      <c r="Y5" s="5"/>
-      <c r="Z5" s="5"/>
-      <c r="AA5" s="5"/>
-      <c r="AB5" s="5"/>
-      <c r="AC5" s="9"/>
-      <c r="AE5" s="29"/>
+      <c r="B5" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="31"/>
+      <c r="D5" s="30"/>
+      <c r="E5" s="30"/>
+      <c r="F5" s="30"/>
+      <c r="G5" s="30"/>
+      <c r="H5" s="35"/>
+      <c r="I5" s="59"/>
+      <c r="J5" s="57"/>
+      <c r="K5" s="57"/>
+      <c r="L5" s="57"/>
+      <c r="M5" s="57"/>
+      <c r="N5" s="57"/>
+      <c r="O5" s="57"/>
+      <c r="P5" s="57"/>
+      <c r="Q5" s="57"/>
+      <c r="R5" s="57"/>
+      <c r="S5" s="57"/>
+      <c r="T5" s="57"/>
+      <c r="U5" s="57"/>
+      <c r="V5" s="57"/>
+      <c r="W5" s="58"/>
+      <c r="X5" s="59"/>
+      <c r="Y5" s="57"/>
+      <c r="Z5" s="57"/>
+      <c r="AA5" s="58"/>
+      <c r="AB5" s="60"/>
+      <c r="AC5" s="58"/>
     </row>
     <row r="6" spans="1:31" ht="13.5" x14ac:dyDescent="0.3">
       <c r="A6" s="1"/>
-      <c r="B6" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" s="23"/>
-      <c r="D6" s="5"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
-      <c r="G6" s="5"/>
-      <c r="H6" s="5"/>
-      <c r="I6" s="5"/>
-      <c r="J6" s="8"/>
-      <c r="K6" s="8"/>
-      <c r="L6" s="5"/>
-      <c r="M6" s="5"/>
-      <c r="N6" s="5"/>
-      <c r="O6" s="5"/>
-      <c r="P6" s="5"/>
-      <c r="Q6" s="5"/>
-      <c r="R6" s="5"/>
-      <c r="S6" s="5"/>
-      <c r="T6" s="5"/>
-      <c r="U6" s="5"/>
-      <c r="V6" s="5"/>
-      <c r="W6" s="5"/>
-      <c r="X6" s="5"/>
-      <c r="Y6" s="5"/>
-      <c r="Z6" s="5"/>
-      <c r="AA6" s="5"/>
-      <c r="AB6" s="5"/>
-      <c r="AC6" s="9"/>
+      <c r="B6" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" s="31"/>
+      <c r="D6" s="30"/>
+      <c r="E6" s="30"/>
+      <c r="F6" s="30"/>
+      <c r="G6" s="30"/>
+      <c r="H6" s="35"/>
+      <c r="I6" s="59"/>
+      <c r="J6" s="57"/>
+      <c r="K6" s="57"/>
+      <c r="L6" s="57"/>
+      <c r="M6" s="57"/>
+      <c r="N6" s="57"/>
+      <c r="O6" s="57"/>
+      <c r="P6" s="57"/>
+      <c r="Q6" s="57"/>
+      <c r="R6" s="57"/>
+      <c r="S6" s="57"/>
+      <c r="T6" s="57"/>
+      <c r="U6" s="57"/>
+      <c r="V6" s="57"/>
+      <c r="W6" s="58"/>
+      <c r="X6" s="59"/>
+      <c r="Y6" s="57"/>
+      <c r="Z6" s="57"/>
+      <c r="AA6" s="58"/>
+      <c r="AB6" s="60"/>
+      <c r="AC6" s="58"/>
+      <c r="AE6" s="10"/>
     </row>
     <row r="7" spans="1:31" ht="13.5" x14ac:dyDescent="0.3">
       <c r="A7" s="1"/>
-      <c r="B7" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" s="23"/>
+      <c r="B7" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" s="8"/>
       <c r="D7" s="5"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="5"/>
-      <c r="H7" s="5"/>
-      <c r="I7" s="5"/>
-      <c r="J7" s="5"/>
-      <c r="K7" s="5"/>
-      <c r="L7" s="5"/>
-      <c r="M7" s="5"/>
-      <c r="N7" s="5"/>
-      <c r="O7" s="5"/>
-      <c r="P7" s="5"/>
-      <c r="Q7" s="5"/>
-      <c r="R7" s="5"/>
-      <c r="S7" s="8"/>
-      <c r="T7" s="8"/>
-      <c r="U7" s="5"/>
-      <c r="V7" s="5"/>
-      <c r="W7" s="5"/>
-      <c r="X7" s="5"/>
-      <c r="Y7" s="5"/>
-      <c r="Z7" s="5"/>
-      <c r="AA7" s="5"/>
-      <c r="AB7" s="5"/>
-      <c r="AC7" s="9"/>
+      <c r="E7" s="57"/>
+      <c r="F7" s="57"/>
+      <c r="G7" s="57"/>
+      <c r="H7" s="58"/>
+      <c r="I7" s="36"/>
+      <c r="J7" s="32"/>
+      <c r="K7" s="32"/>
+      <c r="L7" s="32"/>
+      <c r="M7" s="32"/>
+      <c r="N7" s="32"/>
+      <c r="O7" s="32"/>
+      <c r="P7" s="32"/>
+      <c r="Q7" s="32"/>
+      <c r="R7" s="32"/>
+      <c r="S7" s="32"/>
+      <c r="T7" s="32"/>
+      <c r="U7" s="32"/>
+      <c r="V7" s="32"/>
+      <c r="W7" s="37"/>
+      <c r="X7" s="59"/>
+      <c r="Y7" s="57"/>
+      <c r="Z7" s="57"/>
+      <c r="AA7" s="58"/>
+      <c r="AB7" s="60"/>
+      <c r="AC7" s="58"/>
     </row>
     <row r="8" spans="1:31" ht="13.5" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
-      <c r="B8" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" s="23"/>
+      <c r="B8" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" s="8"/>
       <c r="D8" s="5"/>
-      <c r="E8" s="31"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="5"/>
-      <c r="H8" s="5"/>
-      <c r="I8" s="5"/>
-      <c r="J8" s="5"/>
-      <c r="K8" s="5"/>
-      <c r="L8" s="5"/>
-      <c r="M8" s="5"/>
-      <c r="N8" s="5"/>
-      <c r="O8" s="8"/>
-      <c r="P8" s="5"/>
-      <c r="Q8" s="5"/>
-      <c r="R8" s="5"/>
-      <c r="S8" s="5"/>
-      <c r="T8" s="5"/>
-      <c r="U8" s="5"/>
-      <c r="V8" s="5"/>
-      <c r="W8" s="5"/>
-      <c r="X8" s="5"/>
-      <c r="Y8" s="5"/>
-      <c r="Z8" s="5"/>
-      <c r="AA8" s="5"/>
-      <c r="AB8" s="5"/>
-      <c r="AC8" s="9"/>
+      <c r="E8" s="57"/>
+      <c r="F8" s="57"/>
+      <c r="G8" s="57"/>
+      <c r="H8" s="58"/>
+      <c r="I8" s="36"/>
+      <c r="J8" s="32"/>
+      <c r="K8" s="32"/>
+      <c r="L8" s="32"/>
+      <c r="M8" s="32"/>
+      <c r="N8" s="32"/>
+      <c r="O8" s="32"/>
+      <c r="P8" s="32"/>
+      <c r="Q8" s="32"/>
+      <c r="R8" s="32"/>
+      <c r="S8" s="32"/>
+      <c r="T8" s="32"/>
+      <c r="U8" s="32"/>
+      <c r="V8" s="32"/>
+      <c r="W8" s="37"/>
+      <c r="X8" s="59"/>
+      <c r="Y8" s="57"/>
+      <c r="Z8" s="57"/>
+      <c r="AA8" s="58"/>
+      <c r="AB8" s="60"/>
+      <c r="AC8" s="58"/>
     </row>
     <row r="9" spans="1:31" ht="13.5" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
-      <c r="B9" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="C9" s="23"/>
+      <c r="B9" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="8"/>
       <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5"/>
-      <c r="H9" s="5"/>
-      <c r="I9" s="5"/>
-      <c r="J9" s="8"/>
-      <c r="K9" s="5"/>
-      <c r="L9" s="5"/>
-      <c r="M9" s="5"/>
-      <c r="N9" s="5"/>
-      <c r="O9" s="5"/>
-      <c r="P9" s="5"/>
-      <c r="Q9" s="5"/>
-      <c r="R9" s="5"/>
-      <c r="S9" s="8"/>
-      <c r="T9" s="5"/>
-      <c r="U9" s="5"/>
-      <c r="V9" s="5"/>
-      <c r="W9" s="5"/>
-      <c r="X9" s="5"/>
-      <c r="Y9" s="5"/>
-      <c r="Z9" s="5"/>
-      <c r="AA9" s="5"/>
-      <c r="AB9" s="5"/>
-      <c r="AC9" s="9"/>
+      <c r="E9" s="61"/>
+      <c r="F9" s="57"/>
+      <c r="G9" s="57"/>
+      <c r="H9" s="58"/>
+      <c r="I9" s="36"/>
+      <c r="J9" s="32"/>
+      <c r="K9" s="32"/>
+      <c r="L9" s="32"/>
+      <c r="M9" s="32"/>
+      <c r="N9" s="32"/>
+      <c r="O9" s="32"/>
+      <c r="P9" s="32"/>
+      <c r="Q9" s="32"/>
+      <c r="R9" s="32"/>
+      <c r="S9" s="32"/>
+      <c r="T9" s="32"/>
+      <c r="U9" s="32"/>
+      <c r="V9" s="32"/>
+      <c r="W9" s="37"/>
+      <c r="X9" s="59"/>
+      <c r="Y9" s="57"/>
+      <c r="Z9" s="57"/>
+      <c r="AA9" s="58"/>
+      <c r="AB9" s="60"/>
+      <c r="AC9" s="58"/>
     </row>
     <row r="10" spans="1:31" ht="13.5" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
-      <c r="B10" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="C10" s="23"/>
+      <c r="B10" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" s="8"/>
       <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5"/>
-      <c r="H10" s="5"/>
-      <c r="I10" s="5"/>
-      <c r="J10" s="5"/>
-      <c r="K10" s="5"/>
-      <c r="L10" s="5"/>
-      <c r="M10" s="5"/>
-      <c r="N10" s="5"/>
-      <c r="O10" s="5"/>
-      <c r="P10" s="5"/>
-      <c r="Q10" s="5"/>
-      <c r="R10" s="5"/>
-      <c r="S10" s="5"/>
-      <c r="T10" s="8"/>
-      <c r="U10" s="5"/>
-      <c r="V10" s="5"/>
-      <c r="W10" s="5"/>
-      <c r="X10" s="8"/>
-      <c r="Y10" s="8"/>
-      <c r="Z10" s="5"/>
-      <c r="AA10" s="5"/>
-      <c r="AB10" s="5"/>
-      <c r="AC10" s="9"/>
+      <c r="E10" s="57"/>
+      <c r="F10" s="57"/>
+      <c r="G10" s="57"/>
+      <c r="H10" s="58"/>
+      <c r="I10" s="36"/>
+      <c r="J10" s="32"/>
+      <c r="K10" s="32"/>
+      <c r="L10" s="32"/>
+      <c r="M10" s="32"/>
+      <c r="N10" s="32"/>
+      <c r="O10" s="32"/>
+      <c r="P10" s="32"/>
+      <c r="Q10" s="32"/>
+      <c r="R10" s="32"/>
+      <c r="S10" s="32"/>
+      <c r="T10" s="32"/>
+      <c r="U10" s="32"/>
+      <c r="V10" s="32"/>
+      <c r="W10" s="37"/>
+      <c r="X10" s="59"/>
+      <c r="Y10" s="57"/>
+      <c r="Z10" s="57"/>
+      <c r="AA10" s="58"/>
+      <c r="AB10" s="60"/>
+      <c r="AC10" s="58"/>
     </row>
     <row r="11" spans="1:31" ht="13.5" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
-      <c r="B11" s="14" t="s">
+      <c r="B11" s="38" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="39"/>
+      <c r="D11" s="40"/>
+      <c r="E11" s="62"/>
+      <c r="F11" s="62"/>
+      <c r="G11" s="62"/>
+      <c r="H11" s="63"/>
+      <c r="I11" s="64"/>
+      <c r="J11" s="62"/>
+      <c r="K11" s="62"/>
+      <c r="L11" s="62"/>
+      <c r="M11" s="62"/>
+      <c r="N11" s="62"/>
+      <c r="O11" s="62"/>
+      <c r="P11" s="62"/>
+      <c r="Q11" s="62"/>
+      <c r="R11" s="62"/>
+      <c r="S11" s="62"/>
+      <c r="T11" s="62"/>
+      <c r="U11" s="62"/>
+      <c r="V11" s="62"/>
+      <c r="W11" s="63"/>
+      <c r="X11" s="41"/>
+      <c r="Y11" s="42"/>
+      <c r="Z11" s="42"/>
+      <c r="AA11" s="72"/>
+      <c r="AB11" s="65"/>
+      <c r="AC11" s="63"/>
+    </row>
+    <row r="12" spans="1:31" ht="13.5" x14ac:dyDescent="0.3">
+      <c r="A12" s="1"/>
+      <c r="B12" s="45" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12" s="47"/>
+      <c r="D12" s="43"/>
+      <c r="E12" s="66"/>
+      <c r="F12" s="66"/>
+      <c r="G12" s="66"/>
+      <c r="H12" s="67"/>
+      <c r="I12" s="68"/>
+      <c r="J12" s="66"/>
+      <c r="K12" s="66"/>
+      <c r="L12" s="66"/>
+      <c r="M12" s="66"/>
+      <c r="N12" s="66"/>
+      <c r="O12" s="66"/>
+      <c r="P12" s="66"/>
+      <c r="Q12" s="66"/>
+      <c r="R12" s="66"/>
+      <c r="S12" s="66"/>
+      <c r="T12" s="66"/>
+      <c r="U12" s="66"/>
+      <c r="V12" s="66"/>
+      <c r="W12" s="67"/>
+      <c r="X12" s="73"/>
+      <c r="Y12" s="44"/>
+      <c r="Z12" s="44"/>
+      <c r="AA12" s="48"/>
+      <c r="AB12" s="69"/>
+      <c r="AC12" s="67"/>
+    </row>
+    <row r="13" spans="1:31" ht="14" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="1"/>
+      <c r="B13" s="46" t="s">
         <v>19</v>
       </c>
-      <c r="C11" s="24"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="8"/>
-      <c r="G11" s="8"/>
-      <c r="H11" s="8"/>
-      <c r="I11" s="8"/>
-      <c r="J11" s="8"/>
-      <c r="K11" s="8"/>
-      <c r="L11" s="8"/>
-      <c r="M11" s="8"/>
-      <c r="N11" s="8"/>
-      <c r="O11" s="8"/>
-      <c r="P11" s="8"/>
-      <c r="Q11" s="8"/>
-      <c r="R11" s="8"/>
-      <c r="S11" s="8"/>
-      <c r="T11" s="8"/>
-      <c r="U11" s="8"/>
-      <c r="V11" s="8"/>
-      <c r="W11" s="8"/>
-      <c r="X11" s="8"/>
-      <c r="Y11" s="8"/>
-      <c r="Z11" s="8"/>
-      <c r="AA11" s="8"/>
-      <c r="AB11" s="8"/>
-      <c r="AC11" s="10"/>
-    </row>
-    <row r="12" spans="1:31" ht="14" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="1"/>
-      <c r="B12" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="C12" s="25"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="11"/>
-      <c r="H12" s="11"/>
-      <c r="I12" s="11"/>
-      <c r="J12" s="11"/>
-      <c r="K12" s="11"/>
-      <c r="L12" s="11"/>
-      <c r="M12" s="11"/>
-      <c r="N12" s="11"/>
-      <c r="O12" s="11"/>
-      <c r="P12" s="11"/>
-      <c r="Q12" s="11"/>
-      <c r="R12" s="11"/>
-      <c r="S12" s="11"/>
-      <c r="T12" s="11"/>
-      <c r="U12" s="11"/>
-      <c r="V12" s="11"/>
-      <c r="W12" s="11"/>
-      <c r="X12" s="11"/>
-      <c r="Y12" s="11"/>
-      <c r="Z12" s="11"/>
-      <c r="AA12" s="26"/>
-      <c r="AB12" s="11"/>
-      <c r="AC12" s="12"/>
-    </row>
-    <row r="13" spans="1:31" ht="13.5" x14ac:dyDescent="0.3">
-      <c r="A13" s="1"/>
+      <c r="C13" s="49"/>
+      <c r="D13" s="50"/>
+      <c r="E13" s="50"/>
+      <c r="F13" s="50"/>
+      <c r="G13" s="50"/>
+      <c r="H13" s="51"/>
+      <c r="I13" s="49"/>
+      <c r="J13" s="50"/>
+      <c r="K13" s="50"/>
+      <c r="L13" s="50"/>
+      <c r="M13" s="50"/>
+      <c r="N13" s="50"/>
+      <c r="O13" s="50"/>
+      <c r="P13" s="50"/>
+      <c r="Q13" s="50"/>
+      <c r="R13" s="50"/>
+      <c r="S13" s="50"/>
+      <c r="T13" s="50"/>
+      <c r="U13" s="50"/>
+      <c r="V13" s="50"/>
+      <c r="W13" s="51"/>
+      <c r="X13" s="49"/>
+      <c r="Y13" s="50"/>
+      <c r="Z13" s="50"/>
+      <c r="AA13" s="51"/>
+      <c r="AB13" s="52"/>
+      <c r="AC13" s="51"/>
     </row>
     <row r="14" spans="1:31" ht="13.5" x14ac:dyDescent="0.3">
       <c r="A14" s="1"/>
@@ -4266,20 +4652,26 @@
     <row r="1001" spans="1:1" ht="13.5" x14ac:dyDescent="0.3">
       <c r="A1001" s="1"/>
     </row>
+    <row r="1002" spans="1:1" ht="13.5" x14ac:dyDescent="0.3">
+      <c r="A1002" s="1"/>
+    </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="5">
     <mergeCell ref="B1:F1"/>
     <mergeCell ref="G1:AC1"/>
+    <mergeCell ref="C2:H2"/>
+    <mergeCell ref="I2:W2"/>
+    <mergeCell ref="X2:AA2"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
-  <conditionalFormatting sqref="C3:AC12">
+  <conditionalFormatting sqref="C4:AC13">
     <cfRule type="notContainsBlanks" dxfId="1" priority="1">
-      <formula>LEN(TRIM(C3))&gt;0</formula>
+      <formula>LEN(TRIM(C4))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C3:AC12">
+  <conditionalFormatting sqref="C4:AC13">
     <cfRule type="expression" dxfId="0" priority="3">
-      <formula>AND(#REF!&lt;=C$2,#REF!&gt;=C$2)</formula>
+      <formula>AND(#REF!&lt;=C$3,#REF!&gt;=C$3)</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
